--- a/output/yearly_benthic_cover_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_79_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.47218572229677</v>
+        <v>45.65896432512194</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0595886307032</v>
+        <v>98.58774737179991</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.99830276392117</v>
+        <v>87.86604171320505</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90725213460426</v>
+        <v>45.79188628010898</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228672444600063</v>
+        <v>2.228420154078969</v>
       </c>
       <c r="E3" t="n">
-        <v>5.692549501917576</v>
+        <v>5.61964957833802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428908148666876</v>
+        <v>0.7428067180263229</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96598217182398</v>
+        <v>33.92727449950963</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17297748386763</v>
+        <v>34.16910902921085</v>
       </c>
       <c r="I3" t="n">
-        <v>6.552162753928449</v>
+        <v>6.536239746376734</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643067592916798</v>
+        <v>4.642541987664518</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00169723607883</v>
+        <v>12.13395828679496</v>
       </c>
       <c r="L3" t="n">
-        <v>48.85585544772604</v>
+        <v>48.8395052578349</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7648048184091</v>
+        <v>106.7653498247388</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09526122303321</v>
+        <v>86.93814857841308</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63707599703262</v>
+        <v>42.49806889104664</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185191178032297</v>
+        <v>2.183483597607029</v>
       </c>
       <c r="E4" t="n">
-        <v>6.493416477905067</v>
+        <v>6.416039096612135</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444464979926325</v>
+        <v>0.7443612470693243</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30330788398619</v>
+        <v>33.2431239439263</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2445389076611</v>
+        <v>34.24061736518892</v>
       </c>
       <c r="I4" t="n">
-        <v>5.471569665001972</v>
+        <v>5.458265533826096</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652790612453954</v>
+        <v>4.652257794183276</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90473877696679</v>
+        <v>13.06185142158692</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27618070505813</v>
+        <v>44.25851747218931</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81799547905754</v>
+        <v>99.81843778482288</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.90588339760819</v>
+        <v>85.79743468195079</v>
       </c>
       <c r="C5" t="n">
-        <v>42.29692444374144</v>
+        <v>42.20438642400611</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127046395814038</v>
+        <v>2.127717519775123</v>
       </c>
       <c r="E5" t="n">
-        <v>7.081923170965132</v>
+        <v>7.011608215721495</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745765936232773</v>
+        <v>0.7456789871658518</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41715494527367</v>
+        <v>32.39409597812688</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30523306670756</v>
+        <v>34.30123340962918</v>
       </c>
       <c r="I5" t="n">
-        <v>4.567722781160179</v>
+        <v>4.556606901745675</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661037101454832</v>
+        <v>4.660493669786574</v>
       </c>
       <c r="K5" t="n">
-        <v>14.09411660239182</v>
+        <v>14.20256531804922</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45697090761669</v>
+        <v>43.44142977089394</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84801195374995</v>
+        <v>99.84838151294927</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.52629529705629</v>
+        <v>84.52747143176592</v>
       </c>
       <c r="C6" t="n">
-        <v>41.62670828956155</v>
+        <v>41.64199952029138</v>
       </c>
       <c r="D6" t="n">
-        <v>2.059642753172837</v>
+        <v>2.065751796240945</v>
       </c>
       <c r="E6" t="n">
-        <v>7.492864879264856</v>
+        <v>7.441219615963147</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468870775254115</v>
+        <v>0.7467972500105169</v>
       </c>
       <c r="G6" t="n">
-        <v>31.38989276064256</v>
+        <v>31.45067958151217</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35680556616893</v>
+        <v>34.35267350048377</v>
       </c>
       <c r="I6" t="n">
-        <v>3.812158025747874</v>
+        <v>3.802866874989641</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668044234533823</v>
+        <v>4.66748281256573</v>
       </c>
       <c r="K6" t="n">
-        <v>15.47370470294369</v>
+        <v>15.47252856823409</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77270581912921</v>
+        <v>42.75889949753716</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87311881163446</v>
+        <v>99.87342758606263</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.99315038218877</v>
+        <v>82.97234223412252</v>
       </c>
       <c r="C7" t="n">
-        <v>40.68560894820311</v>
+        <v>40.67749500094304</v>
       </c>
       <c r="D7" t="n">
-        <v>1.985049356234802</v>
+        <v>1.989850208075987</v>
       </c>
       <c r="E7" t="n">
-        <v>7.751641099154965</v>
+        <v>7.696657325253706</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478412690871409</v>
+        <v>0.7477492375207856</v>
       </c>
       <c r="G7" t="n">
-        <v>30.25305544896317</v>
+        <v>30.29509228711992</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40069837800848</v>
+        <v>34.39646492595614</v>
       </c>
       <c r="I7" t="n">
-        <v>3.180856898945592</v>
+        <v>3.173095515691074</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674007931794631</v>
+        <v>4.673432734504909</v>
       </c>
       <c r="K7" t="n">
-        <v>17.00684961781122</v>
+        <v>17.02765776587749</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20164815549265</v>
+        <v>42.18921204220754</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89410672150699</v>
+        <v>99.89436480902806</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.02558770970789</v>
+        <v>87.8681891819944</v>
       </c>
       <c r="C8" t="n">
-        <v>43.07121902005854</v>
+        <v>42.99713683215734</v>
       </c>
       <c r="D8" t="n">
-        <v>1.98933572808587</v>
+        <v>1.994097062455303</v>
       </c>
       <c r="E8" t="n">
-        <v>9.644286847439494</v>
+        <v>9.540724883979577</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494561033756757</v>
+        <v>0.7493451275586923</v>
       </c>
       <c r="G8" t="n">
-        <v>30.78114521290987</v>
+        <v>30.80473675555511</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47498075528108</v>
+        <v>34.46987586769985</v>
       </c>
       <c r="I8" t="n">
-        <v>5.702282416517935</v>
+        <v>5.626002437504036</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684100646097974</v>
+        <v>4.683407047241826</v>
       </c>
       <c r="K8" t="n">
-        <v>11.97441229029209</v>
+        <v>12.1318108180056</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76470216126724</v>
+        <v>44.68391832759913</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81033347161787</v>
+        <v>99.81286597776207</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.12115529613538</v>
+        <v>85.89650478670687</v>
       </c>
       <c r="C9" t="n">
-        <v>42.05177514719922</v>
+        <v>41.89860866169229</v>
       </c>
       <c r="D9" t="n">
-        <v>1.903515120633727</v>
+        <v>1.90470056730035</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02167208731929</v>
+        <v>9.895822268094557</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508370664913395</v>
+        <v>0.7507109513527062</v>
       </c>
       <c r="G9" t="n">
-        <v>29.45323633209651</v>
+        <v>29.42374304568684</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53850505860161</v>
+        <v>34.53270376222449</v>
       </c>
       <c r="I9" t="n">
-        <v>4.760657965422022</v>
+        <v>4.696880746093521</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692731665570873</v>
+        <v>4.691943445954412</v>
       </c>
       <c r="K9" t="n">
-        <v>13.87884470386462</v>
+        <v>14.10349521329312</v>
       </c>
       <c r="L9" t="n">
-        <v>43.910983415144</v>
+        <v>43.84161827952838</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84160326620784</v>
+        <v>99.84372215451378</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.08602427042746</v>
+        <v>83.7240029434202</v>
       </c>
       <c r="C10" t="n">
-        <v>40.75533207603043</v>
+        <v>40.45481953721632</v>
       </c>
       <c r="D10" t="n">
-        <v>1.812744668694197</v>
+        <v>1.80713973602515</v>
       </c>
       <c r="E10" t="n">
-        <v>10.20602562744895</v>
+        <v>10.04231020332329</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520197537260275</v>
+        <v>0.7518826261764844</v>
       </c>
       <c r="G10" t="n">
-        <v>28.04873812561202</v>
+        <v>27.91662697713136</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59290867139726</v>
+        <v>34.58660080411828</v>
       </c>
       <c r="I10" t="n">
-        <v>3.973463962761326</v>
+        <v>3.920176183042606</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700123460787673</v>
+        <v>4.699266413603026</v>
       </c>
       <c r="K10" t="n">
-        <v>15.91397572957256</v>
+        <v>16.27599705657979</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19845169535751</v>
+        <v>43.13871449659017</v>
       </c>
       <c r="M10" t="n">
-        <v>99.8677595009605</v>
+        <v>99.86953109038629</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.90000260618129</v>
+        <v>81.50030165106632</v>
       </c>
       <c r="C11" t="n">
-        <v>39.18537650606301</v>
+        <v>38.83872716461387</v>
       </c>
       <c r="D11" t="n">
-        <v>1.716156915748658</v>
+        <v>1.708367863741181</v>
       </c>
       <c r="E11" t="n">
-        <v>10.21483676054287</v>
+        <v>10.03863037372788</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530345942251631</v>
+        <v>0.7528885719584443</v>
       </c>
       <c r="G11" t="n">
-        <v>26.55422837181294</v>
+        <v>26.39080279241758</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6395913343575</v>
+        <v>34.63287431008844</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3156884155869</v>
+        <v>3.271184164392521</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706466213907269</v>
+        <v>4.705553574740276</v>
       </c>
       <c r="K11" t="n">
-        <v>18.0999973938187</v>
+        <v>18.49969834893368</v>
       </c>
       <c r="L11" t="n">
-        <v>42.6042521011527</v>
+        <v>42.55268070359015</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88962600103442</v>
+        <v>99.8911062171377</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.59494480043701</v>
+        <v>79.16107537971139</v>
       </c>
       <c r="C12" t="n">
-        <v>37.39371111652796</v>
+        <v>37.00579446443357</v>
       </c>
       <c r="D12" t="n">
-        <v>1.615237401969354</v>
+        <v>1.605425951111847</v>
       </c>
       <c r="E12" t="n">
-        <v>10.07519366433581</v>
+        <v>9.888581223643586</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539069697720897</v>
+        <v>0.7537537795310444</v>
       </c>
       <c r="G12" t="n">
-        <v>24.99269294840506</v>
+        <v>24.80055998058803</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67972060951612</v>
+        <v>34.67267385842804</v>
       </c>
       <c r="I12" t="n">
-        <v>2.766274645363001</v>
+        <v>2.729119464339822</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711918561075561</v>
+        <v>4.710961122069026</v>
       </c>
       <c r="K12" t="n">
-        <v>20.40505519956299</v>
+        <v>20.83892462028859</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10913122792051</v>
+        <v>42.06441468848915</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90789754401148</v>
+        <v>99.90913377321132</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.21989712974364</v>
+        <v>76.79156389068227</v>
       </c>
       <c r="C13" t="n">
-        <v>35.44618812564492</v>
+        <v>35.05785381589255</v>
       </c>
       <c r="D13" t="n">
-        <v>1.51216365207491</v>
+        <v>1.502097679056359</v>
       </c>
       <c r="E13" t="n">
-        <v>9.816849065894493</v>
+        <v>9.631552235003392</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546579244266468</v>
+        <v>0.7544986229506809</v>
       </c>
       <c r="G13" t="n">
-        <v>23.39782486337205</v>
+        <v>23.20434870280975</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71426452362575</v>
+        <v>34.70693665573133</v>
       </c>
       <c r="I13" t="n">
-        <v>2.307525072683251</v>
+        <v>2.276513601688998</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716612027666542</v>
+        <v>4.715616393441755</v>
       </c>
       <c r="K13" t="n">
-        <v>22.78010287025636</v>
+        <v>23.20843610931775</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69686804172752</v>
+        <v>41.65790120078026</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92315903762879</v>
+        <v>99.92419112599055</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.69405420539428</v>
+        <v>83.78518002730249</v>
       </c>
       <c r="C14" t="n">
-        <v>39.59082120649646</v>
+        <v>39.29405167311149</v>
       </c>
       <c r="D14" t="n">
-        <v>1.513824978648214</v>
+        <v>1.503966899669795</v>
       </c>
       <c r="E14" t="n">
-        <v>12.1144289764626</v>
+        <v>12.00758636858488</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554870233551154</v>
+        <v>0.7554375261914574</v>
       </c>
       <c r="G14" t="n">
-        <v>25.25057636896675</v>
+        <v>25.0759586650057</v>
       </c>
       <c r="H14" t="n">
-        <v>36.57944874567741</v>
+        <v>36.59286051695611</v>
       </c>
       <c r="I14" t="n">
-        <v>2.758494216314732</v>
+        <v>3.127885512197934</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721793895969471</v>
+        <v>4.721484538696608</v>
       </c>
       <c r="K14" t="n">
-        <v>16.3059457946057</v>
+        <v>16.21481997269751</v>
       </c>
       <c r="L14" t="n">
-        <v>44.01138410074903</v>
+        <v>44.38699508793233</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90815110185119</v>
+        <v>99.89586673374134</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.89586386941053</v>
+        <v>83.07464012635387</v>
       </c>
       <c r="C15" t="n">
-        <v>39.20066017913319</v>
+        <v>39.06683810186402</v>
       </c>
       <c r="D15" t="n">
-        <v>1.481944041497341</v>
+        <v>1.477818878293573</v>
       </c>
       <c r="E15" t="n">
-        <v>12.26138773295122</v>
+        <v>12.23370542707547</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561860043221902</v>
+        <v>0.7562284467951208</v>
       </c>
       <c r="G15" t="n">
-        <v>24.73741107806956</v>
+        <v>24.63998716633388</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63190049294741</v>
+        <v>36.63117215269884</v>
       </c>
       <c r="I15" t="n">
-        <v>2.300871992609129</v>
+        <v>2.609300262687464</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726162527013688</v>
+        <v>4.726427792469504</v>
       </c>
       <c r="K15" t="n">
-        <v>17.10413613058948</v>
+        <v>16.92535987364614</v>
       </c>
       <c r="L15" t="n">
-        <v>43.61857885093524</v>
+        <v>43.92091631581766</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9233751606579</v>
+        <v>99.91311429132782</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.39039464078743</v>
+        <v>80.73899361561141</v>
       </c>
       <c r="C16" t="n">
-        <v>37.05102518274628</v>
+        <v>37.13449622201774</v>
       </c>
       <c r="D16" t="n">
-        <v>1.386557485306358</v>
+        <v>1.389065171895539</v>
       </c>
       <c r="E16" t="n">
-        <v>11.7919931737756</v>
+        <v>11.86171142283473</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567876763864854</v>
+        <v>0.7569079339998409</v>
       </c>
       <c r="G16" t="n">
-        <v>23.14516711625734</v>
+        <v>23.16017782113368</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66104727834501</v>
+        <v>36.66408603325589</v>
       </c>
       <c r="I16" t="n">
-        <v>1.918918933301117</v>
+        <v>2.176370644992722</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729922977415534</v>
+        <v>4.730674587499004</v>
       </c>
       <c r="K16" t="n">
-        <v>19.60960535921255</v>
+        <v>19.2610063843886</v>
       </c>
       <c r="L16" t="n">
-        <v>43.27545634713537</v>
+        <v>43.53201683074123</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9360868890942</v>
+        <v>99.92751943714757</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.11441233178414</v>
+        <v>82.46036058780662</v>
       </c>
       <c r="C17" t="n">
-        <v>38.32042590983133</v>
+        <v>38.36864191237633</v>
       </c>
       <c r="D17" t="n">
-        <v>1.387614715640904</v>
+        <v>1.390305478779406</v>
       </c>
       <c r="E17" t="n">
-        <v>12.57794501524894</v>
+        <v>12.65730242114314</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573647162112059</v>
+        <v>0.7575837828656733</v>
       </c>
       <c r="G17" t="n">
-        <v>23.62672024170909</v>
+        <v>23.59770988251972</v>
       </c>
       <c r="H17" t="n">
-        <v>37.15290606992086</v>
+        <v>37.11367583725436</v>
       </c>
       <c r="I17" t="n">
-        <v>1.878332096733113</v>
+        <v>2.208884542333883</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733529476320037</v>
+        <v>4.734898642910457</v>
       </c>
       <c r="K17" t="n">
-        <v>17.88558766821586</v>
+        <v>17.53963941219337</v>
       </c>
       <c r="L17" t="n">
-        <v>43.73142305573739</v>
+        <v>44.01815487636296</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93743663378459</v>
+        <v>99.92643620093267</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.64705454903992</v>
+        <v>80.2396080108922</v>
       </c>
       <c r="C18" t="n">
-        <v>36.14316636394553</v>
+        <v>36.48893850816208</v>
       </c>
       <c r="D18" t="n">
-        <v>1.297388953703059</v>
+        <v>1.309290509811739</v>
       </c>
       <c r="E18" t="n">
-        <v>12.02114982459601</v>
+        <v>12.22676869247627</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578611825666168</v>
+        <v>0.7581635380102913</v>
       </c>
       <c r="G18" t="n">
-        <v>22.0904589064321</v>
+        <v>22.22263960982056</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17726047602751</v>
+        <v>37.14207777112488</v>
       </c>
       <c r="I18" t="n">
-        <v>1.566302814673257</v>
+        <v>1.842145777084125</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736632391041355</v>
+        <v>4.738522112564319</v>
       </c>
       <c r="K18" t="n">
-        <v>20.35294545096007</v>
+        <v>19.76039198910782</v>
       </c>
       <c r="L18" t="n">
-        <v>43.45171229351849</v>
+        <v>43.68931159877638</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9478241084241</v>
+        <v>99.93864209604628</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.61960648916045</v>
+        <v>79.39099511281826</v>
       </c>
       <c r="C19" t="n">
-        <v>35.35215948184581</v>
+        <v>35.92410303219553</v>
       </c>
       <c r="D19" t="n">
-        <v>1.260239104282461</v>
+        <v>1.279043281924613</v>
       </c>
       <c r="E19" t="n">
-        <v>11.89536888059699</v>
+        <v>12.20032449039282</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582823104492267</v>
+        <v>0.7586525203265854</v>
       </c>
       <c r="G19" t="n">
-        <v>21.45791365493793</v>
+        <v>21.70925221451409</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19791911555894</v>
+        <v>37.16603278651399</v>
       </c>
       <c r="I19" t="n">
-        <v>1.310618983027234</v>
+        <v>1.536111567105017</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739264440307666</v>
+        <v>4.741578252041157</v>
       </c>
       <c r="K19" t="n">
-        <v>21.38039351083957</v>
+        <v>20.60900488718173</v>
       </c>
       <c r="L19" t="n">
-        <v>43.22378397053248</v>
+        <v>43.41572136459263</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95633696321785</v>
+        <v>99.9488292839699</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.0416057401476</v>
+        <v>76.94646296419781</v>
       </c>
       <c r="C20" t="n">
-        <v>32.97583361556311</v>
+        <v>33.71608918730222</v>
       </c>
       <c r="D20" t="n">
-        <v>1.166935706331631</v>
+        <v>1.190849290305182</v>
       </c>
       <c r="E20" t="n">
-        <v>11.1967977880863</v>
+        <v>11.57254157377378</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586455236076866</v>
+        <v>0.7590734556794965</v>
       </c>
       <c r="G20" t="n">
-        <v>19.86924984492137</v>
+        <v>20.21233210639237</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21573671924548</v>
+        <v>37.18665421293535</v>
       </c>
       <c r="I20" t="n">
-        <v>1.092705635407107</v>
+        <v>1.280803227114769</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741534522548041</v>
+        <v>4.744209097996852</v>
       </c>
       <c r="K20" t="n">
-        <v>23.95839425985239</v>
+        <v>23.0535370358022</v>
       </c>
       <c r="L20" t="n">
-        <v>43.02936604172263</v>
+        <v>43.18770401114266</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96359391713814</v>
+        <v>99.95733023424708</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.09555295838555</v>
+        <v>82.71285627986185</v>
       </c>
       <c r="C21" t="n">
-        <v>36.83692692911021</v>
+        <v>37.20589080563751</v>
       </c>
       <c r="D21" t="n">
-        <v>1.167623740509864</v>
+        <v>1.191779812936075</v>
       </c>
       <c r="E21" t="n">
-        <v>13.24819255479156</v>
+        <v>13.48006597425332</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7590928267852084</v>
+        <v>0.7596665912129095</v>
       </c>
       <c r="G21" t="n">
-        <v>21.68373713964045</v>
+        <v>21.80345089146642</v>
       </c>
       <c r="H21" t="n">
-        <v>39.04045163471268</v>
+        <v>38.79103663346083</v>
       </c>
       <c r="I21" t="n">
-        <v>1.452124894538247</v>
+        <v>1.938940181451613</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744330167407552</v>
+        <v>4.747916195080683</v>
       </c>
       <c r="K21" t="n">
-        <v>17.90444704161444</v>
+        <v>17.28714372013813</v>
       </c>
       <c r="L21" t="n">
-        <v>45.21025038877007</v>
+        <v>45.44238459795949</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95162435949473</v>
+        <v>99.93541912373513</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_79_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.65896432512194</v>
+        <v>45.25790219376891</v>
       </c>
       <c r="M2" t="n">
-        <v>98.58774737179991</v>
+        <v>101.5129316168542</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.86604171320505</v>
+        <v>88.01600367502874</v>
       </c>
       <c r="C3" t="n">
-        <v>45.79188628010898</v>
+        <v>45.89879233282446</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228420154078969</v>
+        <v>2.228724284849984</v>
       </c>
       <c r="E3" t="n">
-        <v>5.61964957833802</v>
+        <v>5.688750650612501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428067180263229</v>
+        <v>0.7429080949499948</v>
       </c>
       <c r="G3" t="n">
-        <v>33.92727449950963</v>
+        <v>33.96284743519257</v>
       </c>
       <c r="H3" t="n">
-        <v>34.16910902921085</v>
+        <v>34.17377236769975</v>
       </c>
       <c r="I3" t="n">
-        <v>6.536239746376734</v>
+        <v>6.575825248286471</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642541987664518</v>
+        <v>4.643175593437467</v>
       </c>
       <c r="K3" t="n">
-        <v>12.13395828679496</v>
+        <v>11.98399632497125</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8395052578349</v>
+        <v>48.88117226664931</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7653498247388</v>
+        <v>106.763960924445</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.93814857841308</v>
+        <v>87.10386167406577</v>
       </c>
       <c r="C4" t="n">
-        <v>42.49806889104664</v>
+        <v>42.62439752690409</v>
       </c>
       <c r="D4" t="n">
-        <v>2.183483597607029</v>
+        <v>2.184764855350168</v>
       </c>
       <c r="E4" t="n">
-        <v>6.416039096612135</v>
+        <v>6.491773898552523</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7443612470693243</v>
+        <v>0.7444692899096269</v>
       </c>
       <c r="G4" t="n">
-        <v>33.2431239439263</v>
+        <v>33.29296313968363</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24061736518892</v>
+        <v>34.24558733584283</v>
       </c>
       <c r="I4" t="n">
-        <v>5.458265533826096</v>
+        <v>5.49137009279183</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652257794183276</v>
+        <v>4.652933061935167</v>
       </c>
       <c r="K4" t="n">
-        <v>13.06185142158692</v>
+        <v>12.89613832593422</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25851747218931</v>
+        <v>44.29680233470928</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81843778482288</v>
+        <v>99.81733818754759</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.79743468195079</v>
+        <v>86.0588638686022</v>
       </c>
       <c r="C5" t="n">
-        <v>42.20438642400611</v>
+        <v>42.43166366869792</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127717519775123</v>
+        <v>2.134149185753623</v>
       </c>
       <c r="E5" t="n">
-        <v>7.011608215721495</v>
+        <v>7.105419889322294</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7456789871658518</v>
+        <v>0.7457911937246392</v>
       </c>
       <c r="G5" t="n">
-        <v>32.39409597812688</v>
+        <v>32.5216464380068</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30123340962918</v>
+        <v>34.3063949113334</v>
       </c>
       <c r="I5" t="n">
-        <v>4.556606901745675</v>
+        <v>4.584267289682465</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660493669786574</v>
+        <v>4.661194960778994</v>
       </c>
       <c r="K5" t="n">
-        <v>14.20256531804922</v>
+        <v>13.94113613139779</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44142977089394</v>
+        <v>43.47466214177119</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84838151294927</v>
+        <v>99.8474619418669</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.52747143176592</v>
+        <v>84.82104572822283</v>
       </c>
       <c r="C6" t="n">
-        <v>41.64199952029138</v>
+        <v>41.90589235666162</v>
       </c>
       <c r="D6" t="n">
-        <v>2.065751796240945</v>
+        <v>2.074005879589215</v>
       </c>
       <c r="E6" t="n">
-        <v>7.441219615963147</v>
+        <v>7.542840330971353</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7467972500105169</v>
+        <v>0.7469125240051711</v>
       </c>
       <c r="G6" t="n">
-        <v>31.45067958151217</v>
+        <v>31.6051409979239</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35267350048377</v>
+        <v>34.35797610423786</v>
       </c>
       <c r="I6" t="n">
-        <v>3.802866874989641</v>
+        <v>3.825966616463003</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66748281256573</v>
+        <v>4.668203275032318</v>
       </c>
       <c r="K6" t="n">
-        <v>15.47252856823409</v>
+        <v>15.17895427177719</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75889949753716</v>
+        <v>42.78781261351445</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87342758606263</v>
+        <v>99.87265924195326</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.97234223412252</v>
+        <v>83.37305262365452</v>
       </c>
       <c r="C7" t="n">
-        <v>40.67749500094304</v>
+        <v>41.05229088020785</v>
       </c>
       <c r="D7" t="n">
-        <v>1.989850208075987</v>
+        <v>2.003707015366045</v>
       </c>
       <c r="E7" t="n">
-        <v>7.696657325253706</v>
+        <v>7.819236656280625</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7477492375207856</v>
+        <v>0.7478658395368616</v>
       </c>
       <c r="G7" t="n">
-        <v>30.29509228711992</v>
+        <v>30.53387811596561</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39646492595614</v>
+        <v>34.40182861869563</v>
       </c>
       <c r="I7" t="n">
-        <v>3.173095515691074</v>
+        <v>3.192374880704348</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673432734504909</v>
+        <v>4.674161497105384</v>
       </c>
       <c r="K7" t="n">
-        <v>17.02765776587749</v>
+        <v>16.62694737634551</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18921204220754</v>
+        <v>42.21448489298935</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89436480902806</v>
+        <v>99.89372314954271</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.8681891819944</v>
+        <v>88.26574596843176</v>
       </c>
       <c r="C8" t="n">
-        <v>42.99713683215734</v>
+        <v>43.39236599962557</v>
       </c>
       <c r="D8" t="n">
-        <v>1.994097062455303</v>
+        <v>2.007961372755919</v>
       </c>
       <c r="E8" t="n">
-        <v>9.540724883979577</v>
+        <v>9.676545326285536</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7493451275586923</v>
+        <v>0.7494537406305186</v>
       </c>
       <c r="G8" t="n">
-        <v>30.80473675555511</v>
+        <v>31.05053810804517</v>
       </c>
       <c r="H8" t="n">
-        <v>34.46987586769985</v>
+        <v>34.47487206900386</v>
       </c>
       <c r="I8" t="n">
-        <v>5.626002437504036</v>
+        <v>5.622289472770019</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683407047241826</v>
+        <v>4.684085878940741</v>
       </c>
       <c r="K8" t="n">
-        <v>12.1318108180056</v>
+        <v>11.73425403156823</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68391832759913</v>
+        <v>44.68636739290282</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81286597776207</v>
+        <v>99.81298742409663</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.89650478670687</v>
+        <v>86.26209366971725</v>
       </c>
       <c r="C9" t="n">
-        <v>41.89860866169229</v>
+        <v>42.26171978688735</v>
       </c>
       <c r="D9" t="n">
-        <v>1.90470056730035</v>
+        <v>1.917288365148886</v>
       </c>
       <c r="E9" t="n">
-        <v>9.895822268094557</v>
+        <v>10.02187384644577</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507109513527062</v>
+        <v>0.7508130631973782</v>
       </c>
       <c r="G9" t="n">
-        <v>29.42374304568684</v>
+        <v>29.64839675399658</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53270376222449</v>
+        <v>34.53740090707939</v>
       </c>
       <c r="I9" t="n">
-        <v>4.696880746093521</v>
+        <v>4.693739088865626</v>
       </c>
       <c r="J9" t="n">
-        <v>4.691943445954412</v>
+        <v>4.692581644983614</v>
       </c>
       <c r="K9" t="n">
-        <v>14.10349521329312</v>
+        <v>13.73790633028275</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84161827952838</v>
+        <v>43.84419917525295</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84372215451378</v>
+        <v>99.84382529242305</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.7240029434202</v>
+        <v>84.12340035380042</v>
       </c>
       <c r="C10" t="n">
-        <v>40.45481953721632</v>
+        <v>40.85158691965868</v>
       </c>
       <c r="D10" t="n">
-        <v>1.80713973602515</v>
+        <v>1.821512498984146</v>
       </c>
       <c r="E10" t="n">
-        <v>10.04231020332329</v>
+        <v>10.17416318379422</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7518826261764844</v>
+        <v>0.7519785438650917</v>
       </c>
       <c r="G10" t="n">
-        <v>27.91662697713136</v>
+        <v>28.16734626043175</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58660080411828</v>
+        <v>34.59101301779421</v>
       </c>
       <c r="I10" t="n">
-        <v>3.920176183042606</v>
+        <v>3.917520949774191</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699266413603026</v>
+        <v>4.699865899156823</v>
       </c>
       <c r="K10" t="n">
-        <v>16.27599705657979</v>
+        <v>15.87659964619957</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13871449659017</v>
+        <v>43.14143179278436</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86953109038629</v>
+        <v>99.86961835864261</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.50030165106632</v>
+        <v>81.81095691845508</v>
       </c>
       <c r="C11" t="n">
-        <v>38.83872716461387</v>
+        <v>39.14665718364294</v>
       </c>
       <c r="D11" t="n">
-        <v>1.708367863741181</v>
+        <v>1.718922719333395</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03863037372788</v>
+        <v>10.14596687423644</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7528885719584443</v>
+        <v>0.7529801128337301</v>
       </c>
       <c r="G11" t="n">
-        <v>26.39080279241758</v>
+        <v>26.58092736524674</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63287431008844</v>
+        <v>34.63708519035158</v>
       </c>
       <c r="I11" t="n">
-        <v>3.271184164392521</v>
+        <v>3.268948951242376</v>
       </c>
       <c r="J11" t="n">
-        <v>4.705553574740276</v>
+        <v>4.706125705210813</v>
       </c>
       <c r="K11" t="n">
-        <v>18.49969834893368</v>
+        <v>18.18904308154492</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55268070359015</v>
+        <v>42.55547970842953</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8911062171377</v>
+        <v>99.8911799736174</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.16107537971139</v>
+        <v>79.3328150250463</v>
       </c>
       <c r="C12" t="n">
-        <v>37.00579446443357</v>
+        <v>37.17467586591408</v>
       </c>
       <c r="D12" t="n">
-        <v>1.605425951111847</v>
+        <v>1.609967099260101</v>
       </c>
       <c r="E12" t="n">
-        <v>9.888581223643586</v>
+        <v>9.957395663017778</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7537537795310444</v>
+        <v>0.7538429595606206</v>
       </c>
       <c r="G12" t="n">
-        <v>24.80055998058803</v>
+        <v>24.89606894163665</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67267385842804</v>
+        <v>34.67677613978854</v>
       </c>
       <c r="I12" t="n">
-        <v>2.729119464339822</v>
+        <v>2.727245724528728</v>
       </c>
       <c r="J12" t="n">
-        <v>4.710961122069026</v>
+        <v>4.711518497253879</v>
       </c>
       <c r="K12" t="n">
-        <v>20.83892462028859</v>
+        <v>20.6671849749537</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06441468848915</v>
+        <v>42.06733502159771</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90913377321132</v>
+        <v>99.90919586246548</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.79156389068227</v>
+        <v>76.96085000132834</v>
       </c>
       <c r="C13" t="n">
-        <v>35.05785381589255</v>
+        <v>35.22409376816395</v>
       </c>
       <c r="D13" t="n">
-        <v>1.502097679056359</v>
+        <v>1.50672105871837</v>
       </c>
       <c r="E13" t="n">
-        <v>9.631552235003392</v>
+        <v>9.697992342818786</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7544986229506809</v>
+        <v>0.7545857400830827</v>
       </c>
       <c r="G13" t="n">
-        <v>23.20434870280975</v>
+        <v>23.2995018164704</v>
       </c>
       <c r="H13" t="n">
-        <v>34.70693665573133</v>
+        <v>34.7109440438218</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276513601688998</v>
+        <v>2.274944123896628</v>
       </c>
       <c r="J13" t="n">
-        <v>4.715616393441755</v>
+        <v>4.716160875519266</v>
       </c>
       <c r="K13" t="n">
-        <v>23.20843610931775</v>
+        <v>23.03914999867167</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65790120078026</v>
+        <v>41.66099940748303</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92419112599055</v>
+        <v>99.92424317431865</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.78518002730249</v>
+        <v>83.69977779451004</v>
       </c>
       <c r="C14" t="n">
-        <v>39.29405167311149</v>
+        <v>39.47997565152458</v>
       </c>
       <c r="D14" t="n">
-        <v>1.503966899669795</v>
+        <v>1.508417070399035</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00758636858488</v>
+        <v>12.05740941746546</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554375261914574</v>
+        <v>0.7554351250583828</v>
       </c>
       <c r="G14" t="n">
-        <v>25.0759586650057</v>
+        <v>25.20315391648746</v>
       </c>
       <c r="H14" t="n">
-        <v>36.59286051695611</v>
+        <v>36.62744121506078</v>
       </c>
       <c r="I14" t="n">
-        <v>3.127885512197934</v>
+        <v>2.826451518424042</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721484538696608</v>
+        <v>4.721469531614892</v>
       </c>
       <c r="K14" t="n">
-        <v>16.21481997269751</v>
+        <v>16.30022220548994</v>
       </c>
       <c r="L14" t="n">
-        <v>44.38699508793233</v>
+        <v>44.1256930244968</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89586673374134</v>
+        <v>99.90589088151134</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.07464012635387</v>
+        <v>82.92027011733809</v>
       </c>
       <c r="C15" t="n">
-        <v>39.06683810186402</v>
+        <v>39.1374705631306</v>
       </c>
       <c r="D15" t="n">
-        <v>1.477818878293573</v>
+        <v>1.479488959684905</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23370542707547</v>
+        <v>12.21910967122609</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562284467951208</v>
+        <v>0.7561510820087821</v>
       </c>
       <c r="G15" t="n">
-        <v>24.63998716633388</v>
+        <v>24.71981304137489</v>
       </c>
       <c r="H15" t="n">
-        <v>36.63117215269884</v>
+        <v>36.66215454813652</v>
       </c>
       <c r="I15" t="n">
-        <v>2.609300262687464</v>
+        <v>2.35760855235201</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726427792469504</v>
+        <v>4.725944262554888</v>
       </c>
       <c r="K15" t="n">
-        <v>16.92535987364614</v>
+        <v>17.07972988266191</v>
       </c>
       <c r="L15" t="n">
-        <v>43.92091631581766</v>
+        <v>43.70428701202905</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91311429132782</v>
+        <v>99.92148745782156</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.73899361561141</v>
+        <v>80.50436573177345</v>
       </c>
       <c r="C16" t="n">
-        <v>37.13449622201774</v>
+        <v>37.08610400100115</v>
       </c>
       <c r="D16" t="n">
-        <v>1.389065171895539</v>
+        <v>1.387581515283767</v>
       </c>
       <c r="E16" t="n">
-        <v>11.86171142283473</v>
+        <v>11.78775766614571</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569079339998409</v>
+        <v>0.7567667006737611</v>
       </c>
       <c r="G16" t="n">
-        <v>23.16017782113368</v>
+        <v>23.18419168520706</v>
       </c>
       <c r="H16" t="n">
-        <v>36.66408603325589</v>
+        <v>36.6920029569733</v>
       </c>
       <c r="I16" t="n">
-        <v>2.176370644992722</v>
+        <v>1.966273328278848</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730674587499004</v>
+        <v>4.729791879211007</v>
       </c>
       <c r="K16" t="n">
-        <v>19.2610063843886</v>
+        <v>19.49563426822655</v>
       </c>
       <c r="L16" t="n">
-        <v>43.53201683074123</v>
+        <v>43.35277260431808</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92751943714757</v>
+        <v>99.93451087354578</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.46036058780662</v>
+        <v>82.10661725501244</v>
       </c>
       <c r="C17" t="n">
-        <v>38.36864191237633</v>
+        <v>38.26557582205908</v>
       </c>
       <c r="D17" t="n">
-        <v>1.390305478779406</v>
+        <v>1.388676182041391</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65730242114314</v>
+        <v>12.53408484457533</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575837828656733</v>
+        <v>0.7573637159419664</v>
       </c>
       <c r="G17" t="n">
-        <v>23.59770988251972</v>
+        <v>23.61563889430792</v>
       </c>
       <c r="H17" t="n">
-        <v>37.11367583725436</v>
+        <v>37.13410651440727</v>
       </c>
       <c r="I17" t="n">
-        <v>2.208884542333883</v>
+        <v>1.943223879101251</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734898642910457</v>
+        <v>4.73352322463729</v>
       </c>
       <c r="K17" t="n">
-        <v>17.53963941219337</v>
+        <v>17.89338274498758</v>
       </c>
       <c r="L17" t="n">
-        <v>44.01815487636296</v>
+        <v>43.77631836385176</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92643620093267</v>
+        <v>99.93527693089843</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.2396080108922</v>
+        <v>79.67505399356506</v>
       </c>
       <c r="C18" t="n">
-        <v>36.48893850816208</v>
+        <v>36.13409258084997</v>
       </c>
       <c r="D18" t="n">
-        <v>1.309290509811739</v>
+        <v>1.299604645575092</v>
       </c>
       <c r="E18" t="n">
-        <v>12.22676869247627</v>
+        <v>12.00020715602448</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581635380102913</v>
+        <v>0.7578771643278127</v>
       </c>
       <c r="G18" t="n">
-        <v>22.22263960982056</v>
+        <v>22.1009004202476</v>
       </c>
       <c r="H18" t="n">
-        <v>37.14207777112488</v>
+        <v>37.15928127080018</v>
       </c>
       <c r="I18" t="n">
-        <v>1.842145777084125</v>
+        <v>1.620451059541073</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738522112564319</v>
+        <v>4.736732277048829</v>
       </c>
       <c r="K18" t="n">
-        <v>19.76039198910782</v>
+        <v>20.32494600643495</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68931159877638</v>
+        <v>43.48698297162893</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93864209604628</v>
+        <v>99.94602155891386</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.39099511281826</v>
+        <v>78.63477449119105</v>
       </c>
       <c r="C19" t="n">
-        <v>35.92410303219553</v>
+        <v>35.34326262975812</v>
       </c>
       <c r="D19" t="n">
-        <v>1.279043281924613</v>
+        <v>1.262132525433452</v>
       </c>
       <c r="E19" t="n">
-        <v>12.20032449039282</v>
+        <v>11.8794087625557</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586525203265854</v>
+        <v>0.7583112750272023</v>
       </c>
       <c r="G19" t="n">
-        <v>21.70925221451409</v>
+        <v>21.46365462507005</v>
       </c>
       <c r="H19" t="n">
-        <v>37.16603278651399</v>
+        <v>37.18056604139436</v>
       </c>
       <c r="I19" t="n">
-        <v>1.536111567105017</v>
+        <v>1.351255792790275</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741578252041157</v>
+        <v>4.739445468920014</v>
       </c>
       <c r="K19" t="n">
-        <v>20.60900488718173</v>
+        <v>21.36522550880896</v>
       </c>
       <c r="L19" t="n">
-        <v>43.41572136459263</v>
+        <v>43.2464957868012</v>
       </c>
       <c r="M19" t="n">
-        <v>99.9488292839699</v>
+        <v>99.95498392536827</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.94646296419781</v>
+        <v>75.9795592852392</v>
       </c>
       <c r="C20" t="n">
-        <v>33.71608918730222</v>
+        <v>32.89596639779989</v>
       </c>
       <c r="D20" t="n">
-        <v>1.190849290305182</v>
+        <v>1.165866562632969</v>
       </c>
       <c r="E20" t="n">
-        <v>11.57254157377378</v>
+        <v>11.16110411158632</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590734556794965</v>
+        <v>0.7586860757427576</v>
       </c>
       <c r="G20" t="n">
-        <v>20.21233210639237</v>
+        <v>19.82656871209129</v>
       </c>
       <c r="H20" t="n">
-        <v>37.18665421293535</v>
+        <v>37.19894279935113</v>
       </c>
       <c r="I20" t="n">
-        <v>1.280803227114769</v>
+        <v>1.126603050442519</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744209097996852</v>
+        <v>4.741787973392234</v>
       </c>
       <c r="K20" t="n">
-        <v>23.0535370358022</v>
+        <v>24.0204407147608</v>
       </c>
       <c r="L20" t="n">
-        <v>43.18770401114266</v>
+        <v>43.04605800430626</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95733023424708</v>
+        <v>99.96246511686694</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.71285627986185</v>
+        <v>81.81076758433764</v>
       </c>
       <c r="C21" t="n">
-        <v>37.20589080563751</v>
+        <v>36.55626110688375</v>
       </c>
       <c r="D21" t="n">
-        <v>1.191779812936075</v>
+        <v>1.166612959504468</v>
       </c>
       <c r="E21" t="n">
-        <v>13.48006597425332</v>
+        <v>13.12237355957099</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7596665912129095</v>
+        <v>0.7591717924890256</v>
       </c>
       <c r="G21" t="n">
-        <v>21.80345089146642</v>
+        <v>21.5315063989549</v>
       </c>
       <c r="H21" t="n">
-        <v>38.79103663346083</v>
+        <v>38.91500241567464</v>
       </c>
       <c r="I21" t="n">
-        <v>1.938940181451613</v>
+        <v>1.571276755087196</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747916195080683</v>
+        <v>4.744823703056408</v>
       </c>
       <c r="K21" t="n">
-        <v>17.28714372013813</v>
+        <v>18.18923241566236</v>
       </c>
       <c r="L21" t="n">
-        <v>45.44238459795949</v>
+        <v>45.20216409561898</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93541912373513</v>
+        <v>99.9476576181651</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_79_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_79_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.25790219376891</v>
+        <v>43.8351617225706</v>
       </c>
       <c r="M2" t="n">
-        <v>101.5129316168542</v>
+        <v>93.00681688003314</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01600367502874</v>
+        <v>81.54377698239321</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89879233282446</v>
+        <v>43.29933253794879</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228724284849984</v>
+        <v>2.183457727409458</v>
       </c>
       <c r="E3" t="n">
-        <v>5.688750650612501</v>
+        <v>4.162341074193271</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429080949499948</v>
+        <v>0.7376801427751506</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96284743519257</v>
+        <v>32.8428433164506</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17377236769975</v>
+        <v>33.93328656765692</v>
       </c>
       <c r="I3" t="n">
-        <v>6.575825248286471</v>
+        <v>3.073667261563128</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643175593437467</v>
+        <v>4.610500892344691</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98399632497125</v>
+        <v>18.45622301760677</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88117226664931</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.763960924445</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.10386167406577</v>
+        <v>88.68202998615541</v>
       </c>
       <c r="C4" t="n">
-        <v>42.62439752690409</v>
+        <v>42.91326486075821</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184764855350168</v>
+        <v>2.189211157523189</v>
       </c>
       <c r="E4" t="n">
-        <v>6.491773898552523</v>
+        <v>6.559314226910414</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444692899096269</v>
+        <v>0.7396239363711818</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29296313968363</v>
+        <v>33.53819236632336</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24558733584283</v>
+        <v>34.02270107307436</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49137009279183</v>
+        <v>7.010337623633018</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652933061935167</v>
+        <v>4.622649602319886</v>
       </c>
       <c r="K4" t="n">
-        <v>12.89613832593422</v>
+        <v>11.3179700138446</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29680233470928</v>
+        <v>45.53570132973925</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81733818754759</v>
+        <v>99.76693620434206</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.0588638686022</v>
+        <v>87.64053386327117</v>
       </c>
       <c r="C5" t="n">
-        <v>42.43166366869792</v>
+        <v>42.95850356752629</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134149185753623</v>
+        <v>2.140047265727148</v>
       </c>
       <c r="E5" t="n">
-        <v>7.105419889322294</v>
+        <v>7.387835605847791</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457911937246392</v>
+        <v>0.7412709925967151</v>
       </c>
       <c r="G5" t="n">
-        <v>32.5216464380068</v>
+        <v>32.78501327947905</v>
       </c>
       <c r="H5" t="n">
-        <v>34.3063949113334</v>
+        <v>34.09846565944889</v>
       </c>
       <c r="I5" t="n">
-        <v>4.584267289682465</v>
+        <v>5.854957356442108</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661194960778994</v>
+        <v>4.632943703729469</v>
       </c>
       <c r="K5" t="n">
-        <v>13.94113613139779</v>
+        <v>12.35946613672884</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47466214177119</v>
+        <v>44.48729869508843</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8474619418669</v>
+        <v>99.80526839934355</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.82104572822283</v>
+        <v>86.41713364398426</v>
       </c>
       <c r="C6" t="n">
-        <v>41.90589235666162</v>
+        <v>42.64395544609187</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074005879589215</v>
+        <v>2.082090211843572</v>
       </c>
       <c r="E6" t="n">
-        <v>7.542840330971353</v>
+        <v>8.002479062036043</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469125240051711</v>
+        <v>0.7426687007534968</v>
       </c>
       <c r="G6" t="n">
-        <v>31.6051409979239</v>
+        <v>31.89712504839042</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35797610423786</v>
+        <v>34.16276023466084</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825966616463003</v>
+        <v>4.888331006590523</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668203275032318</v>
+        <v>4.641679379709354</v>
       </c>
       <c r="K6" t="n">
-        <v>15.17895427177719</v>
+        <v>13.58286635601575</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78781261351445</v>
+        <v>43.61054049354678</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87265924195326</v>
+        <v>99.8373622956544</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.37305262365452</v>
+        <v>84.98376663872175</v>
       </c>
       <c r="C7" t="n">
-        <v>41.05229088020785</v>
+        <v>41.96993087978748</v>
       </c>
       <c r="D7" t="n">
-        <v>2.003707015366045</v>
+        <v>2.01422041853219</v>
       </c>
       <c r="E7" t="n">
-        <v>7.819236656280625</v>
+        <v>8.421644040987262</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478658395368616</v>
+        <v>0.7438572350565184</v>
       </c>
       <c r="G7" t="n">
-        <v>30.53387811596561</v>
+        <v>30.85737601544881</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40182861869563</v>
+        <v>34.21743281259984</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192374880704348</v>
+        <v>4.080128396993883</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674161497105384</v>
+        <v>4.649107719103238</v>
       </c>
       <c r="K7" t="n">
-        <v>16.62694737634551</v>
+        <v>15.01623336127827</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21448489298935</v>
+        <v>42.87804878652896</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89372314954271</v>
+        <v>99.8642130275947</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.26574596843176</v>
+        <v>83.35121379310766</v>
       </c>
       <c r="C8" t="n">
-        <v>43.39236599962557</v>
+        <v>40.97122936399319</v>
       </c>
       <c r="D8" t="n">
-        <v>2.007961372755919</v>
+        <v>1.937221153628287</v>
       </c>
       <c r="E8" t="n">
-        <v>9.676545326285536</v>
+        <v>8.667159008188325</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494537406305186</v>
+        <v>0.7448700729152968</v>
       </c>
       <c r="G8" t="n">
-        <v>31.05053810804517</v>
+        <v>29.67776565692394</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47487206900386</v>
+        <v>34.26402335410365</v>
       </c>
       <c r="I8" t="n">
-        <v>5.622289472770019</v>
+        <v>3.404736591627571</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684085878940741</v>
+        <v>4.655437955720603</v>
       </c>
       <c r="K8" t="n">
-        <v>11.73425403156823</v>
+        <v>16.64878620689235</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68636739290282</v>
+        <v>42.26664752919798</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81298742409663</v>
+        <v>99.88666310008352</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.26209366971725</v>
+        <v>81.68429872192725</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26171978688735</v>
+        <v>39.83298090264593</v>
       </c>
       <c r="D9" t="n">
-        <v>1.917288365148886</v>
+        <v>1.859209661541343</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02187384644577</v>
+        <v>8.791562549991307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508130631973782</v>
+        <v>0.7457335008314766</v>
       </c>
       <c r="G9" t="n">
-        <v>29.64839675399658</v>
+        <v>28.48264821957454</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53740090707939</v>
+        <v>34.30374103824792</v>
       </c>
       <c r="I9" t="n">
-        <v>4.693739088865626</v>
+        <v>2.840569371543924</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692581644983614</v>
+        <v>4.660834380196727</v>
       </c>
       <c r="K9" t="n">
-        <v>13.73790633028275</v>
+        <v>18.31570127807276</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84419917525295</v>
+        <v>41.75674180284722</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84382529242305</v>
+        <v>99.90542398356592</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.12340035380042</v>
+        <v>86.36401526186393</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85158691965868</v>
+        <v>43.06093533346245</v>
       </c>
       <c r="D10" t="n">
-        <v>1.821512498984146</v>
+        <v>1.861287402700061</v>
       </c>
       <c r="E10" t="n">
-        <v>10.17416318379422</v>
+        <v>10.63534416081446</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519785438650917</v>
+        <v>0.7465668878454124</v>
       </c>
       <c r="G10" t="n">
-        <v>28.16734626043175</v>
+        <v>29.86585919962591</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59101301779421</v>
+        <v>35.6934573223477</v>
       </c>
       <c r="I10" t="n">
-        <v>3.917520949774191</v>
+        <v>2.895457239496564</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699865899156823</v>
+        <v>4.666043049033826</v>
       </c>
       <c r="K10" t="n">
-        <v>15.87659964619957</v>
+        <v>13.63598473813607</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14143179278436</v>
+        <v>43.20667242632445</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86961835864261</v>
+        <v>99.90359249792297</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.81095691845508</v>
+        <v>86.29710915581951</v>
       </c>
       <c r="C11" t="n">
-        <v>39.14665718364294</v>
+        <v>43.3400978640932</v>
       </c>
       <c r="D11" t="n">
-        <v>1.718922719333395</v>
+        <v>1.85093658133509</v>
       </c>
       <c r="E11" t="n">
-        <v>10.14596687423644</v>
+        <v>11.03564960711315</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529801128337301</v>
+        <v>0.7472791212176919</v>
       </c>
       <c r="G11" t="n">
-        <v>26.58092736524674</v>
+        <v>29.74757950479329</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63708519035158</v>
+        <v>35.7753168812808</v>
       </c>
       <c r="I11" t="n">
-        <v>3.268948951242376</v>
+        <v>2.469852952468913</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706125705210813</v>
+        <v>4.670494507610573</v>
       </c>
       <c r="K11" t="n">
-        <v>18.18904308154492</v>
+        <v>13.70289084418049</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55547970842953</v>
+        <v>42.87476132738653</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8911799736174</v>
+        <v>99.91775003566022</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.3328150250463</v>
+        <v>84.6299542918528</v>
       </c>
       <c r="C12" t="n">
-        <v>37.17467586591408</v>
+        <v>42.05732508277986</v>
       </c>
       <c r="D12" t="n">
-        <v>1.609967099260101</v>
+        <v>1.780001053497056</v>
       </c>
       <c r="E12" t="n">
-        <v>9.957395663017778</v>
+        <v>10.95603142110549</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538429595606206</v>
+        <v>0.7478854100257402</v>
       </c>
       <c r="G12" t="n">
-        <v>24.89606894163665</v>
+        <v>28.60752950234842</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67677613978854</v>
+        <v>35.80434241352658</v>
       </c>
       <c r="I12" t="n">
-        <v>2.727245724528728</v>
+        <v>2.059880678688638</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711518497253879</v>
+        <v>4.674283812660875</v>
       </c>
       <c r="K12" t="n">
-        <v>20.6671849749537</v>
+        <v>15.37004570814721</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06733502159771</v>
+        <v>42.50402218261546</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90919586246548</v>
+        <v>99.93139297354254</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.96085000132834</v>
+        <v>85.87609647033032</v>
       </c>
       <c r="C13" t="n">
-        <v>35.22409376816395</v>
+        <v>43.0938452310714</v>
       </c>
       <c r="D13" t="n">
-        <v>1.50672105871837</v>
+        <v>1.781312892446749</v>
       </c>
       <c r="E13" t="n">
-        <v>9.697992342818786</v>
+        <v>11.62389825659604</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545857400830827</v>
+        <v>0.7484365924022062</v>
       </c>
       <c r="G13" t="n">
-        <v>23.2995018164704</v>
+        <v>28.97195712513622</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7109440438218</v>
+        <v>36.17407399918114</v>
       </c>
       <c r="I13" t="n">
-        <v>2.274944123896628</v>
+        <v>1.89868890205418</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716160875519266</v>
+        <v>4.677728702513788</v>
       </c>
       <c r="K13" t="n">
-        <v>23.03914999867167</v>
+        <v>14.1239035296697</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66099940748303</v>
+        <v>42.71900821852122</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92424317431865</v>
+        <v>99.9367569792623</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.69977779451004</v>
+        <v>84.18641049655112</v>
       </c>
       <c r="C14" t="n">
-        <v>39.47997565152458</v>
+        <v>41.699625684754</v>
       </c>
       <c r="D14" t="n">
-        <v>1.508417070399035</v>
+        <v>1.711359533851088</v>
       </c>
       <c r="E14" t="n">
-        <v>12.05740941746546</v>
+        <v>11.43129203630513</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554351250583828</v>
+        <v>0.7489057691652871</v>
       </c>
       <c r="G14" t="n">
-        <v>25.20315391648746</v>
+        <v>27.83420883027659</v>
       </c>
       <c r="H14" t="n">
-        <v>36.62744121506078</v>
+        <v>36.196750649573</v>
       </c>
       <c r="I14" t="n">
-        <v>2.826451518424042</v>
+        <v>1.583232620096979</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721469531614892</v>
+        <v>4.680661057283043</v>
       </c>
       <c r="K14" t="n">
-        <v>16.30022220548994</v>
+        <v>15.81358950344888</v>
       </c>
       <c r="L14" t="n">
-        <v>44.1256930244968</v>
+        <v>42.43404345340674</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90589088151134</v>
+        <v>99.94725864160962</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.92027011733809</v>
+        <v>83.47735303463588</v>
       </c>
       <c r="C15" t="n">
-        <v>39.1374705631306</v>
+        <v>41.21793583079071</v>
       </c>
       <c r="D15" t="n">
-        <v>1.479488959684905</v>
+        <v>1.681739233345967</v>
       </c>
       <c r="E15" t="n">
-        <v>12.21910967122609</v>
+        <v>11.45646185189867</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561510820087821</v>
+        <v>0.7493059336841783</v>
       </c>
       <c r="G15" t="n">
-        <v>24.71981304137489</v>
+        <v>27.35245288503708</v>
       </c>
       <c r="H15" t="n">
-        <v>36.66215454813652</v>
+        <v>36.21609174147734</v>
       </c>
       <c r="I15" t="n">
-        <v>2.35760855235201</v>
+        <v>1.338139303666544</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725944262554888</v>
+        <v>4.683162085526114</v>
       </c>
       <c r="K15" t="n">
-        <v>17.07972988266191</v>
+        <v>16.5226469653641</v>
       </c>
       <c r="L15" t="n">
-        <v>43.70428701202905</v>
+        <v>42.21483638136168</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92148745782156</v>
+        <v>99.95541917751649</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.50436573177345</v>
+        <v>81.35658164392194</v>
       </c>
       <c r="C16" t="n">
-        <v>37.08610400100115</v>
+        <v>39.30504119431674</v>
       </c>
       <c r="D16" t="n">
-        <v>1.387581515283767</v>
+        <v>1.594383541498082</v>
       </c>
       <c r="E16" t="n">
-        <v>11.78775766614571</v>
+        <v>11.04730891954431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567667006737611</v>
+        <v>0.7496484362055713</v>
       </c>
       <c r="G16" t="n">
-        <v>23.18419168520706</v>
+        <v>25.93166635753532</v>
       </c>
       <c r="H16" t="n">
-        <v>36.6920029569733</v>
+        <v>36.23264586467168</v>
       </c>
       <c r="I16" t="n">
-        <v>1.966273328278848</v>
+        <v>1.115625798182147</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729791879211007</v>
+        <v>4.68530272628482</v>
       </c>
       <c r="K16" t="n">
-        <v>19.49563426822655</v>
+        <v>18.64341835607805</v>
       </c>
       <c r="L16" t="n">
-        <v>43.35277260431808</v>
+        <v>42.01436991339224</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93451087354578</v>
+        <v>99.96282946378705</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.10661725501244</v>
+        <v>85.56997771866911</v>
       </c>
       <c r="C17" t="n">
-        <v>38.26557582205908</v>
+        <v>42.07984577087347</v>
       </c>
       <c r="D17" t="n">
-        <v>1.388676182041391</v>
+        <v>1.595164373629674</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53408484457533</v>
+        <v>12.53658097647684</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573637159419664</v>
+        <v>0.7500155684363999</v>
       </c>
       <c r="G17" t="n">
-        <v>23.61563889430792</v>
+        <v>27.21869300263763</v>
       </c>
       <c r="H17" t="n">
-        <v>37.13410651440727</v>
+        <v>37.52471730331123</v>
       </c>
       <c r="I17" t="n">
-        <v>1.943223879101251</v>
+        <v>1.257209191449852</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73352322463729</v>
+        <v>4.687597302727498</v>
       </c>
       <c r="K17" t="n">
-        <v>17.89338274498758</v>
+        <v>14.43002228133089</v>
       </c>
       <c r="L17" t="n">
-        <v>43.77631836385176</v>
+        <v>43.44824548818882</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93527693089843</v>
+        <v>99.95811354039317</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.67505399356506</v>
+        <v>87.18214489372096</v>
       </c>
       <c r="C18" t="n">
-        <v>36.13409258084997</v>
+        <v>42.79663736640939</v>
       </c>
       <c r="D18" t="n">
-        <v>1.299604645575092</v>
+        <v>1.596448074500406</v>
       </c>
       <c r="E18" t="n">
-        <v>12.00020715602448</v>
+        <v>13.12809788101936</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578771643278127</v>
+        <v>0.75061913986401</v>
       </c>
       <c r="G18" t="n">
-        <v>22.1009004202476</v>
+        <v>27.3559126594645</v>
       </c>
       <c r="H18" t="n">
-        <v>37.15928127080018</v>
+        <v>37.55491513939168</v>
       </c>
       <c r="I18" t="n">
-        <v>1.620451059541073</v>
+        <v>2.104782375330954</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736732277048829</v>
+        <v>4.691369624150061</v>
       </c>
       <c r="K18" t="n">
-        <v>20.32494600643495</v>
+        <v>12.81785510627904</v>
       </c>
       <c r="L18" t="n">
-        <v>43.48698297162893</v>
+        <v>44.31540452985117</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94602155891386</v>
+        <v>99.9298970025396</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.63477449119105</v>
+        <v>84.79010679484658</v>
       </c>
       <c r="C19" t="n">
-        <v>35.34326262975812</v>
+        <v>40.7313705414365</v>
       </c>
       <c r="D19" t="n">
-        <v>1.262132525433452</v>
+        <v>1.506737910001633</v>
       </c>
       <c r="E19" t="n">
-        <v>11.8794087625557</v>
+        <v>12.68291539851505</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583112750272023</v>
+        <v>0.7511370789861652</v>
       </c>
       <c r="G19" t="n">
-        <v>21.46365462507005</v>
+        <v>25.81868544619443</v>
       </c>
       <c r="H19" t="n">
-        <v>37.18056604139436</v>
+        <v>37.58082862700063</v>
       </c>
       <c r="I19" t="n">
-        <v>1.351255792790275</v>
+        <v>1.755195590485123</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739445468920014</v>
+        <v>4.694606743663531</v>
       </c>
       <c r="K19" t="n">
-        <v>21.36522550880896</v>
+        <v>15.20989320515343</v>
       </c>
       <c r="L19" t="n">
-        <v>43.2464957868012</v>
+        <v>44.00027007631754</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95498392536827</v>
+        <v>99.94153382290747</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.9795592852392</v>
+        <v>82.3446027159989</v>
       </c>
       <c r="C20" t="n">
-        <v>32.89596639779989</v>
+        <v>38.55774892019475</v>
       </c>
       <c r="D20" t="n">
-        <v>1.165866562632969</v>
+        <v>1.415476857177908</v>
       </c>
       <c r="E20" t="n">
-        <v>11.16110411158632</v>
+        <v>12.15865016181344</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586860757427576</v>
+        <v>0.7515820833793307</v>
       </c>
       <c r="G20" t="n">
-        <v>19.82656871209129</v>
+        <v>24.25488300868775</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19894279935113</v>
+        <v>37.60309305024064</v>
       </c>
       <c r="I20" t="n">
-        <v>1.126603050442519</v>
+        <v>1.463529533579006</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741787973392234</v>
+        <v>4.697388021120815</v>
       </c>
       <c r="K20" t="n">
-        <v>24.0204407147608</v>
+        <v>17.65539728400111</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04605800430626</v>
+        <v>43.7380983627351</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96246511686694</v>
+        <v>99.95124456693097</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.81076758433764</v>
+        <v>79.82788265868518</v>
       </c>
       <c r="C21" t="n">
-        <v>36.55626110688375</v>
+        <v>36.26714004451954</v>
       </c>
       <c r="D21" t="n">
-        <v>1.166612959504468</v>
+        <v>1.321980066527868</v>
       </c>
       <c r="E21" t="n">
-        <v>13.12237355957099</v>
+        <v>11.55890384553484</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591717924890256</v>
+        <v>0.7519650333370866</v>
       </c>
       <c r="G21" t="n">
-        <v>21.5315063989549</v>
+        <v>22.65277011831819</v>
       </c>
       <c r="H21" t="n">
-        <v>38.91500241567464</v>
+        <v>37.62225277106626</v>
       </c>
       <c r="I21" t="n">
-        <v>1.571276755087196</v>
+        <v>1.220229365544122</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744823703056408</v>
+        <v>4.69978145835679</v>
       </c>
       <c r="K21" t="n">
-        <v>18.18923241566236</v>
+        <v>20.17211734131485</v>
       </c>
       <c r="L21" t="n">
-        <v>45.20216409561898</v>
+        <v>43.52008901601063</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9476576181651</v>
+        <v>99.95934640184501</v>
       </c>
     </row>
   </sheetData>
